--- a/laporan_keuangan.xlsx
+++ b/laporan_keuangan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,15 +456,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BBM</t>
+          <t>Minuman</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12500</v>
+        <v>14000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bensin Pertalite</t>
+          <t>belikopi</t>
         </is>
       </c>
     </row>
@@ -476,21 +476,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pemasukan</t>
+          <t>Pengeluaran</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>harian</t>
+          <t>BBM</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7200</v>
+        <v>12500</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">argo shopeefood
-</t>
+          <t>Bensin Pertalite</t>
         </is>
       </c>
     </row>
@@ -507,15 +506,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Transfer</t>
+          <t>harian</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20000</v>
+        <v>7200</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulanan Ortu
+          <t xml:space="preserve">argo shopeefood
 </t>
         </is>
       </c>
@@ -528,18 +527,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Pemasukan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bulanan Ortu
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Pengeluaran</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Makan</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>15000</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Pecel Lele</t>
         </is>
